--- a/Firmware/Modules/McuPowerPath/McuPowerPath_State_Machine.xlsx
+++ b/Firmware/Modules/McuPowerPath/McuPowerPath_State_Machine.xlsx
@@ -68,7 +68,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -525,7 +525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -634,7 +634,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>McuPowerPath_Validation.xlsx</t>
+          <t>McuPowerPath_Board_Validation.xlsx</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/McuPowerPath/McuPowerPath_State_Machine.xlsx
+++ b/Firmware/Modules/McuPowerPath/McuPowerPath_State_Machine.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>چهار حالت مسیر تغذیهٔ خود میکرو</t>
+          <t>حالت‌های مسیر تغذیهٔ خود میکرو</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>ولتاژ ورودی ≥ ۲۲۰۰۰ میلی‌ولت</t>
+          <t>مجوز مشترک اشمیت Fault درست است (پنجرهٔ q33/q34 + حاشیه‌های q169/q170؛ پیش‌فرض برگشت ۲۱۵۰۰..۲۷۵۰۰ میلی‌ولت)</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ولتاژ بین ۲۱۵۰۰ و ۲۱۹۹۹ میلی‌ولت</t>
+          <t>داخل پنجرهٔ خام ولی بیرون باند برگشت (پیش‌فرض ۲۱۰۰۰..۲۱۴۹۹ یا ۲۷۵۰۱..۲۸۰۰۰)؛ مجوز مشترک false</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>ورودی ۵ ثانیه پایدار بالای ۲۲ ولت و تأیید پایهٔ حضور</t>
+          <t>مجوز مشترک ۵ ثانیه درست مانده و پایهٔ حضور تأیید می‌کند</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>ولتاژ ورودی &lt; ۲۱۵۰۰ میلی‌ولت، یا وقفهٔ سخت‌افزاری قطع ورودی</t>
+          <t>مجوز مشترک افتاده (بیرون پنجرهٔ خام q33/q34؛ پیش‌فرض &lt;۲۱۰۰۰ یا &gt;۲۸۰۰۰)، یا وقفهٔ سخت‌افزاری قطع ورودی</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">

--- a/Firmware/Modules/McuPowerPath/McuPowerPath_State_Machine.xlsx
+++ b/Firmware/Modules/McuPowerPath/McuPowerPath_State_Machine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
